--- a/Team-Data/2014-15/1-1-2014-15.xlsx
+++ b/Team-Data/2014-15/1-1-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -751,7 +818,7 @@
         <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>15</v>
@@ -778,7 +845,7 @@
         <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -787,7 +854,7 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
@@ -808,10 +875,10 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -930,7 +997,7 @@
         <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -942,10 +1009,10 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -996,7 +1063,7 @@
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1103,34 +1170,34 @@
         <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN4" t="n">
         <v>22</v>
@@ -1148,16 +1215,16 @@
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1303,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1321,7 +1388,7 @@
         <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>21</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
         <v>19</v>
@@ -1360,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.697</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1407,34 +1474,34 @@
         <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L6" t="n">
         <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O6" t="n">
         <v>21.2</v>
       </c>
       <c r="P6" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="R6" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S6" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T6" t="n">
         <v>45.6</v>
@@ -1443,49 +1510,49 @@
         <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W6" t="n">
         <v>5.8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z6" t="n">
         <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
       <c r="AC6" t="n">
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
         <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1494,10 +1561,10 @@
         <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
         <v>4</v>
@@ -1521,16 +1588,16 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1670,22 +1737,22 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -1697,7 +1764,7 @@
         <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.719</v>
+        <v>0.697</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
         <v>0.478</v>
@@ -1780,31 +1847,31 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.355</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>12.3</v>
@@ -1813,7 +1880,7 @@
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1822,28 +1889,28 @@
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.9</v>
+        <v>109.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1864,13 +1931,13 @@
         <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
@@ -1879,7 +1946,7 @@
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
         <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.394</v>
+        <v>0.406</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,79 +2020,79 @@
         <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>87.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T9" t="n">
-        <v>46.1</v>
+        <v>45.8</v>
       </c>
       <c r="U9" t="n">
         <v>20.8</v>
       </c>
       <c r="V9" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB9" t="n">
         <v>101.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>15</v>
@@ -2034,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>12</v>
@@ -2049,7 +2116,7 @@
         <v>6</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>22</v>
@@ -2064,7 +2131,7 @@
         <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV9" t="n">
         <v>19</v>
@@ -2073,10 +2140,10 @@
         <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2085,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2225,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2258,7 +2325,7 @@
         <v>17</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2437,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="AX11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY11" t="n">
         <v>5</v>
@@ -2446,7 +2513,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H12" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.43</v>
@@ -2508,19 +2575,19 @@
         <v>11.9</v>
       </c>
       <c r="M12" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="R12" t="n">
         <v>12.2</v>
@@ -2529,46 +2596,46 @@
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
         <v>7</v>
@@ -2580,7 +2647,7 @@
         <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,22 +2656,22 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2619,22 +2686,22 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2765,13 +2832,13 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN13" t="n">
         <v>20</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -2938,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
         <v>20</v>
@@ -2956,19 +3023,19 @@
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>25</v>
@@ -2983,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.323</v>
+        <v>0.313</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>87.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M15" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
@@ -3087,40 +3154,40 @@
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>103</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
       </c>
       <c r="AH15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI15" t="n">
         <v>12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>10</v>
       </c>
       <c r="AJ15" t="n">
         <v>2</v>
@@ -3129,19 +3196,19 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
@@ -3150,10 +3217,10 @@
         <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>16</v>
@@ -3165,7 +3232,7 @@
         <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3308,7 +3375,7 @@
         <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3320,7 +3387,7 @@
         <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
@@ -3335,13 +3402,13 @@
         <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>10</v>
@@ -3359,7 +3426,7 @@
         <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
         <v>13</v>
@@ -3532,7 +3599,7 @@
         <v>30</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3663,25 +3730,25 @@
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
         <v>9</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3755,85 +3822,85 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>0.161</v>
+        <v>0.167</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J19" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P19" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.72</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S19" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
         <v>22.5</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10.1</v>
+        <v>-10.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3845,13 +3912,13 @@
         <v>28</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>16</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3863,25 +3930,25 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU19" t="n">
         <v>12</v>
@@ -3899,7 +3966,7 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6.6</v>
@@ -3967,76 +4034,76 @@
         <v>19.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.753</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T20" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
         <v>101.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK20" t="n">
         <v>16</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
         <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,25 +4139,25 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>6</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BA20" t="n">
         <v>27</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4212,7 +4279,7 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ21" t="n">
         <v>19</v>
@@ -4242,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>29</v>
@@ -4257,19 +4324,19 @@
         <v>21</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
         <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4388,10 +4455,10 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>18</v>
@@ -4412,7 +4479,7 @@
         <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
@@ -4421,7 +4488,7 @@
         <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
         <v>5</v>
@@ -4436,7 +4503,7 @@
         <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.382</v>
+        <v>0.371</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.374</v>
       </c>
       <c r="O23" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="P23" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
@@ -4543,40 +4610,40 @@
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG23" t="n">
         <v>22</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>21</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -4585,7 +4652,7 @@
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4600,43 +4667,43 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR23" t="n">
         <v>27</v>
       </c>
-      <c r="AR23" t="n">
-        <v>28</v>
-      </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4816,7 @@
         <v>30</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4779,19 +4846,19 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>28</v>
@@ -4803,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4946,7 +5013,7 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4973,19 +5040,19 @@
         <v>20</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5164,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5211,106 +5278,106 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.424</v>
+        <v>0.406</v>
       </c>
       <c r="H27" t="n">
         <v>48.8</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.461</v>
+        <v>0.458</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O27" t="n">
         <v>23.8</v>
       </c>
       <c r="P27" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R27" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S27" t="n">
         <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
         <v>6.2</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
         <v>25.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>102.2</v>
+        <v>101.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
         <v>19</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH27" t="n">
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
@@ -5349,19 +5416,19 @@
         <v>26</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5393,64 +5460,64 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.576</v>
+        <v>0.588</v>
       </c>
       <c r="H28" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="I28" t="n">
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.368</v>
+        <v>0.373</v>
       </c>
       <c r="O28" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="T28" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U28" t="n">
         <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.6</v>
@@ -5465,13 +5532,13 @@
         <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5486,31 +5553,31 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5525,28 +5592,28 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC28" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>3</v>
@@ -5671,7 +5738,7 @@
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5695,7 +5762,7 @@
         <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5704,13 +5771,13 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV29" t="n">
         <v>1</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5880,10 +5947,10 @@
         <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -6017,25 +6084,25 @@
         <v>2.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
         <v>6</v>
       </c>
       <c r="AG31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH31" t="n">
         <v>12</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>3</v>
@@ -6065,7 +6132,7 @@
         <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU31" t="n">
         <v>4</v>
@@ -6080,13 +6147,13 @@
         <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>23</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-1-2014-15</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
